--- a/data/evaluation_dataset.xlsx
+++ b/data/evaluation_dataset.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI EVAL_files\Evaluation_AI_course\Lecture5.Agents\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI EVAL_files\ai-agent-real-estate-eval\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{058CB38E-C6F3-4796-968D-F8A2E8110FD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565DD423-D459-4F09-B625-CE0B0BA5E9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15960" xr2:uid="{BF369E15-F991-6B4A-BC00-4B14A4CF84E4}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>question</t>
   </si>
@@ -63,42 +63,12 @@
     <t>extract_offers, filter_offers, normalize_offers_currency</t>
   </si>
   <si>
-    <t>Покажи квартиры с keyword "studio" дешевле 2000 долларов.</t>
-  </si>
-  <si>
-    <t>Извлечь объявления и отфильтровать по ключевому слову studio и верхней границе цены 2000 USD.</t>
-  </si>
-  <si>
     <t>Покажи квартиры с keyword "pet friendly" и переведи цены в евро.</t>
   </si>
   <si>
     <t>Извлечь объявления, применить текстовый фильтр pet friendly и затем конвертировать цены в EUR.</t>
   </si>
   <si>
-    <t>Найди объявления от 1000 до 2500 долларов.</t>
-  </si>
-  <si>
-    <t>Извлечь объявления и отфильтровать их по диапазону цен min=1000 и max=2500 USD.</t>
-  </si>
-  <si>
-    <t>Найди квартиры дешевле 2200 долларов и посчитай статистику по найденным ценам.</t>
-  </si>
-  <si>
-    <t>Извлечь объявления, отфильтровать по максимальной цене 2200 USD и вернуть статистику min, max, avg, median по отфильтрованному набору.</t>
-  </si>
-  <si>
-    <t>extract_offers, filter_offers, compute_stats</t>
-  </si>
-  <si>
-    <t>Извлеки объявления с сайта и сразу посчитай статистику по ценам.</t>
-  </si>
-  <si>
-    <t>Извлечь объявления со страницы и вернуть статистику min, max, avg, median по всем извлечённым ценам.</t>
-  </si>
-  <si>
-    <t>extract_offers, compute_stats</t>
-  </si>
-  <si>
     <t>Найди квартиры дешевле 1800 долларов, переведи цены в евро и посчитай статистику.</t>
   </si>
   <si>
@@ -108,116 +78,29 @@
     <t>extract_offers, filter_offers, normalize_offers_currency, compute_stats</t>
   </si>
   <si>
-    <t>Извлеки объявления с сайта, запомни результат и покажи список.</t>
-  </si>
-  <si>
-    <t>Вернуть извлечённые объявления и сохранить их как текущий набор в сессии для следующих запросов.</t>
-  </si>
-  <si>
-    <t>Найди квартиры дешевле 100 долларов.</t>
-  </si>
-  <si>
-    <t>Если подходящих объявлений нет, вернуть корректное сообщение о пустом результате без ошибки выполнения.</t>
-  </si>
-  <si>
-    <t>Найди квартиры дороже 1000000 долларов.</t>
-  </si>
-  <si>
-    <t>Вернуть либо очень малый список, либо сообщение об отсутствии результатов; агент не должен падать на экстремальном фильтре.</t>
-  </si>
-  <si>
-    <t>Покажи статистику по ценам.</t>
-  </si>
-  <si>
-    <t>Если в текущей сессии нет ранее сохранённых объявлений, агент должен корректно сообщить, что сначала нужно извлечь или передать данные.</t>
-  </si>
-  <si>
-    <t>compute_stats</t>
-  </si>
-  <si>
-    <t>Переведи цены в рубли.</t>
-  </si>
-  <si>
-    <t>Если в сессии нет сохранённого списка объявлений, агент должен корректно сообщить о нехватке данных вместо ложного успешного ответа.</t>
-  </si>
-  <si>
-    <t>normalize_offers_currency</t>
-  </si>
-  <si>
-    <t>Найди квартиры дешевле 2000.</t>
-  </si>
-  <si>
-    <t>Агент должен либо явно уточнить или предположить валюту, либо корректно обработать неоднозначность значения цены.</t>
-  </si>
-  <si>
-    <t>Найди квартиры дешевле двух тысяч долларов.</t>
-  </si>
-  <si>
-    <t>Агент должен корректно интерпретировать текстовое числовое значение или сообщить о невозможности надёжно распарсить условие.</t>
-  </si>
-  <si>
-    <t>Найди квартиры с keyword "___________unlikely_keyword___________".</t>
-  </si>
-  <si>
-    <t>Вернуть пустой результат или сообщение, что объявления по такому ключевому слову не найдены, без галлюцинированных офферов.</t>
-  </si>
-  <si>
-    <t>Извлеки объявления с сайта по ссылке и покажи 1000 объектов.</t>
-  </si>
-  <si>
-    <t>Агент должен обработать слишком большой limit безопасно: либо ограничить выдачу разумным числом, либо извлечь доступное количество без ошибки.</t>
-  </si>
-  <si>
-    <t>Извлеки объявления с сайта по ссылке и запомни результат в сессии.</t>
-  </si>
-  <si>
-    <t>Сохранить исходный набор объявлений в памяти текущей сессии для последующих запросов.</t>
-  </si>
-  <si>
-    <t>В этой же сессии покажи только квартиры дешевле 3000 долларов.</t>
-  </si>
-  <si>
-    <t>Использовать сохранённый набор объявлений из сессии и вернуть подмножество офферов с ценой ниже 3000 USD.</t>
-  </si>
-  <si>
-    <t>filter_offers</t>
-  </si>
-  <si>
-    <t>В этой же сессии теперь покажи только квартиры дешевле 2000 долларов.</t>
-  </si>
-  <si>
-    <t>Вернуть набор объявлений, который является подмножеством результата с порогом 3000; проверяется монотонность при ужесточении фильтра.</t>
-  </si>
-  <si>
-    <t>В этой же сессии переведи найденные квартиры в рубли.</t>
-  </si>
-  <si>
-    <t>Состав объявлений должен сохраниться, измениться должна только валюта и числовые значения цен.</t>
-  </si>
-  <si>
-    <t>В этой же сессии посчитай статистику по текущему набору.</t>
-  </si>
-  <si>
-    <t>Статистика min, max, avg, median должна считаться по текущему набору объявлений, полученному в этой сессии после фильтрации и конвертации.</t>
-  </si>
-  <si>
-    <t>Извлеки объявления с сайта по ссылке, затем найди квартиры дешевле 2500 долларов с keyword "studio".</t>
-  </si>
-  <si>
-    <t>Извлечь объявления и затем отфильтровать их по цене до 2500 USD и ключевому слову studio; результат используется как базовый для сравнения.</t>
-  </si>
-  <si>
-    <t>Найди studio квартиры до 2500 USD по той же ссылке.</t>
-  </si>
-  <si>
-    <t>Вернуть результат, семантически эквивалентный предыдущему кейсу, с той же логикой фильтра и тем же порядком инструментов, несмотря на переформулировку запроса.</t>
+    <t>case_id</t>
+  </si>
+  <si>
+    <t>RE-001</t>
+  </si>
+  <si>
+    <t>RE-002</t>
+  </si>
+  <si>
+    <t>RE-003</t>
+  </si>
+  <si>
+    <t>RE-004</t>
+  </si>
+  <si>
+    <t>RE-005</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -238,6 +121,12 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -261,11 +150,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -600,300 +488,99 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EDC4434-C022-2E46-9566-42A800F46AB5}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="49.75" customWidth="1"/>
-    <col min="4" max="4" width="44.625" customWidth="1"/>
+    <col min="2" max="4" width="49.75" customWidth="1"/>
+    <col min="5" max="5" width="44.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/evaluation_dataset.xlsx
+++ b/data/evaluation_dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI EVAL_files\ai-agent-real-estate-eval\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565DD423-D459-4F09-B625-CE0B0BA5E9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435BC37B-55EF-4646-AD39-6D3E05FAF224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15960" xr2:uid="{BF369E15-F991-6B4A-BC00-4B14A4CF84E4}"/>
   </bookViews>
@@ -66,15 +66,9 @@
     <t>Покажи квартиры с keyword "pet friendly" и переведи цены в евро.</t>
   </si>
   <si>
-    <t>Извлечь объявления, применить текстовый фильтр pet friendly и затем конвертировать цены в EUR.</t>
-  </si>
-  <si>
     <t>Найди квартиры дешевле 1800 долларов, переведи цены в евро и посчитай статистику.</t>
   </si>
   <si>
-    <t>Извлечь объявления, отфильтровать по максимальной цене 1800 USD, конвертировать результат в EUR и вычислить min, max, avg, median по полученным ценам.</t>
-  </si>
-  <si>
     <t>extract_offers, filter_offers, normalize_offers_currency, compute_stats</t>
   </si>
   <si>
@@ -94,6 +88,19 @@
   </si>
   <si>
     <t>RE-005</t>
+  </si>
+  <si>
+    <t>Применить текстовый фильтр «pet friendly». Если подходящих объявлений
+нет, корректно сообщить об отсутствии результатов и не придумывать
+объявления, цены или ссылки. Если объявления найдены, конвертировать
+их цены в EUR и вывести реальные ссылки.</t>
+  </si>
+  <si>
+    <t>Отфильтровать объявления по цене ниже 1800 USD. Если подходящих
+объявлений нет, корректно сообщить об отсутствии результатов и не
+выводить ссылки, цены или вымышленную статистику. Если объявления
+найдены, конвертировать цены в EUR и показать минимум, максимум,
+среднее и медиану.</t>
   </si>
 </sst>
 </file>
@@ -150,10 +157,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -491,13 +501,15 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="49.75" customWidth="1"/>
+    <col min="2" max="2" width="49.75" customWidth="1"/>
+    <col min="3" max="3" width="67" customWidth="1"/>
+    <col min="4" max="4" width="49.75" customWidth="1"/>
     <col min="5" max="5" width="44.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -511,7 +523,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -525,7 +537,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -539,7 +551,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -551,29 +563,29 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="63" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
-        <v>13</v>
+      <c r="C6" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
